--- a/data/your_data.xlsx
+++ b/data/your_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\product to github\horng-en\horng-en\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083A37A3-D4F3-42F0-BC1D-6A8E163A7D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DBEF8B-DD50-4EF0-93A6-EBB0B540EC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D43A32C1-A61F-4A54-95F8-3C2BF7724CD0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="700">
   <si>
     <t>IKEA</t>
   </si>
@@ -1925,35 +1925,6 @@
   </si>
   <si>
     <t>瑞振</t>
-  </si>
-  <si>
-    <r>
-      <t>新耐衝(kg-cm/cm</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>舊牌號</t>
@@ -2238,6 +2209,70 @@
   </si>
   <si>
     <t>PP (灰紫口)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20(220/10kg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>36(220/10kg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新耐衝下限(kg-cm/cm2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新耐衝上限(kg-cm/cm2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>G-P1024-03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PP(黑+纖)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>220-300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>130-210</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>320-400</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000-24000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑞振</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5-20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1008-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P2035-02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PP黑什色</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三達</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2302,11 +2337,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2644,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1518570-A4E3-4D17-962D-F7C87800F03E}">
-  <dimension ref="A1:S240"/>
+  <dimension ref="A1:S242"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.25" style="1" bestFit="1" customWidth="1"/>
@@ -2663,61 +2701,61 @@
   <sheetData>
     <row r="1" spans="1:19" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>672</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -2730,6 +2768,12 @@
       <c r="C2" s="1" t="s">
         <v>263</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>685</v>
+      </c>
       <c r="H2" s="1">
         <v>17</v>
       </c>
@@ -2881,7 +2925,7 @@
         <v>68</v>
       </c>
       <c r="K5" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L5" s="1">
         <v>0.94499999999999995</v>
@@ -3802,7 +3846,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>27</v>
@@ -3832,10 +3876,10 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="R26" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="S26" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -4230,13 +4274,13 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>634</v>
       </c>
       <c r="D36" s="1">
         <v>0.06</v>
@@ -4268,10 +4312,10 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D37" s="1">
         <v>0.06</v>
@@ -5190,13 +5234,13 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>638</v>
       </c>
       <c r="D54" s="1">
         <v>0.15</v>
@@ -5558,7 +5602,7 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>59</v>
@@ -5606,7 +5650,7 @@
         <v>30</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
@@ -6479,10 +6523,10 @@
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="D82" s="1">
         <v>0.5</v>
@@ -6587,7 +6631,7 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D85" s="1">
         <v>0.5</v>
@@ -6692,7 +6736,7 @@
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>97</v>
@@ -7558,7 +7602,7 @@
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>112</v>
@@ -7588,7 +7632,7 @@
         <v>1.06</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="S107" s="1" t="s">
         <v>170</v>
@@ -7596,10 +7640,10 @@
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>648</v>
       </c>
       <c r="D108" s="1">
         <v>4</v>
@@ -7635,7 +7679,7 @@
         <v>160</v>
       </c>
       <c r="S108" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
@@ -7981,7 +8025,7 @@
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>112</v>
@@ -8017,7 +8061,7 @@
         <v>0.98</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
@@ -8771,7 +8815,7 @@
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>112</v>
@@ -9742,7 +9786,7 @@
         <v>507</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D155" s="1">
         <v>4</v>
@@ -10030,10 +10074,10 @@
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>653</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>654</v>
       </c>
       <c r="D161" s="1">
         <v>10</v>
@@ -10124,7 +10168,7 @@
         <v>518</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>174</v>
@@ -10346,7 +10390,7 @@
     </row>
     <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>202</v>
@@ -10863,10 +10907,10 @@
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>657</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>658</v>
       </c>
       <c r="D180" s="1">
         <v>5</v>
@@ -11465,10 +11509,10 @@
     </row>
     <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B193" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>659</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>660</v>
       </c>
       <c r="D193" s="1">
         <v>18</v>
@@ -12933,7 +12977,7 @@
     </row>
     <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B225" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>242</v>
@@ -12966,7 +13010,7 @@
         <v>414</v>
       </c>
       <c r="S225" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="226" spans="1:19" x14ac:dyDescent="0.25">
@@ -13552,7 +13596,7 @@
         <v>261</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D239" s="1">
         <v>30</v>
@@ -13590,16 +13634,16 @@
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B240" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C240" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="C240" s="1" t="s">
+      <c r="D240" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="D240" s="1" t="s">
+      <c r="E240" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="E240" s="1" t="s">
-        <v>681</v>
       </c>
       <c r="F240" s="1">
         <v>23.22</v>
@@ -13620,7 +13664,95 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="S240" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B241" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D241" s="1">
+        <v>6</v>
+      </c>
+      <c r="E241" s="1">
+        <v>8</v>
+      </c>
+      <c r="H241" s="1">
+        <v>12</v>
+      </c>
+      <c r="I241" s="1">
+        <v>20</v>
+      </c>
+      <c r="J241" s="1">
+        <v>69</v>
+      </c>
+      <c r="K241" s="1">
+        <v>72</v>
+      </c>
+      <c r="L241" s="1">
+        <v>1.03</v>
+      </c>
+      <c r="M241" s="1">
+        <v>1.06</v>
+      </c>
+      <c r="N241" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="O241" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="P241" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="Q241" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="R241" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="S241" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D242" s="1">
+        <v>4</v>
+      </c>
+      <c r="E242" s="1">
+        <v>7</v>
+      </c>
+      <c r="F242" s="1">
+        <v>7.84</v>
+      </c>
+      <c r="G242" s="1">
+        <v>12.31</v>
+      </c>
+      <c r="J242" s="1">
+        <v>67</v>
+      </c>
+      <c r="K242" s="1">
+        <v>68</v>
+      </c>
+      <c r="L242" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="M242" s="1">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="S242" s="1" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>

--- a/data/your_data.xlsx
+++ b/data/your_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\product to github\horng-en\horng-en\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DBEF8B-DD50-4EF0-93A6-EBB0B540EC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9F8FF0-4A60-4F5A-AED2-EA7ABCBAE53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D43A32C1-A61F-4A54-95F8-3C2BF7724CD0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="714">
   <si>
     <t>IKEA</t>
   </si>
@@ -369,9 +369,6 @@
   </si>
   <si>
     <t>P0503</t>
-  </si>
-  <si>
-    <t>P0508(H)</t>
   </si>
   <si>
     <t>P1003-43</t>
@@ -1318,9 +1315,6 @@
   </si>
   <si>
     <t>11000-13500</t>
-  </si>
-  <si>
-    <t>P0508(C)</t>
   </si>
   <si>
     <t>PP (本霧)</t>
@@ -2273,6 +2267,70 @@
   </si>
   <si>
     <t>三達</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P9023-03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PP(磁白色)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>240-300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10500-12500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>美濃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P0508B(C)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P0508B(H)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P0508-01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P0508-01(C)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B3022T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B3022-05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE (黑)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.00(5kg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.40(5kg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.40(5kg)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.50(kg)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2682,7 +2740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1518570-A4E3-4D17-962D-F7C87800F03E}">
-  <dimension ref="A1:S242"/>
+  <dimension ref="A1:S244"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.25" style="1" bestFit="1" customWidth="1"/>
@@ -2701,78 +2759,78 @@
   <sheetData>
     <row r="1" spans="1:19" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>670</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H2" s="1">
         <v>17</v>
@@ -2784,30 +2842,30 @@
         <v>1.06</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="D3" s="1">
         <v>3</v>
@@ -2828,16 +2886,16 @@
         <v>1.07</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>0</v>
@@ -2845,10 +2903,10 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -2881,16 +2939,16 @@
         <v>0.96</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>2</v>
@@ -2901,7 +2959,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -2934,16 +2992,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>2</v>
@@ -2954,13 +3012,13 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="D6" s="1">
         <v>0.06</v>
@@ -2990,22 +3048,22 @@
         <v>0.96</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -3013,16 +3071,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.13</v>
+      <c r="D7" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>713</v>
       </c>
       <c r="F7" s="1">
         <v>18.559999999999999</v>
@@ -3046,16 +3104,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>2</v>
@@ -3069,7 +3127,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
@@ -3110,7 +3168,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
@@ -3145,10 +3203,10 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
@@ -3181,19 +3239,19 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>9</v>
@@ -3201,10 +3259,10 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -3237,7 +3295,7 @@
         <v>0.96</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -3245,7 +3303,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
@@ -3278,13 +3336,13 @@
         <v>0.96</v>
       </c>
       <c r="N12" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>9</v>
@@ -3295,7 +3353,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>6</v>
@@ -3328,19 +3386,19 @@
         <v>0.98</v>
       </c>
       <c r="N13" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="P13" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>9</v>
@@ -3351,7 +3409,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
@@ -3389,7 +3447,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -3430,7 +3488,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
@@ -3466,7 +3524,7 @@
         <v>0.97</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -3474,7 +3532,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
@@ -3518,7 +3576,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
@@ -3554,7 +3612,7 @@
         <v>0.97</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -3562,7 +3620,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
@@ -3606,7 +3664,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
@@ -3644,10 +3702,10 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>6</v>
@@ -3685,10 +3743,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -3729,7 +3787,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>27</v>
@@ -3770,7 +3828,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>27</v>
@@ -3811,7 +3869,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>27</v>
@@ -3846,7 +3904,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>27</v>
@@ -3876,10 +3934,10 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -3887,7 +3945,7 @@
         <v>28</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>27</v>
@@ -3925,7 +3983,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>27</v>
@@ -3963,10 +4021,10 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>27</v>
@@ -3999,22 +4057,22 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N29" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q29" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -4022,7 +4080,7 @@
         <v>31</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>27</v>
@@ -4055,16 +4113,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N30" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P30" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q30" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>30</v>
@@ -4078,7 +4136,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>27</v>
@@ -4116,7 +4174,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>27</v>
@@ -4154,7 +4212,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>27</v>
@@ -4192,10 +4250,10 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>27</v>
@@ -4233,10 +4291,10 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>27</v>
@@ -4269,18 +4327,18 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>631</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="D36" s="1">
         <v>0.06</v>
@@ -4312,10 +4370,10 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D37" s="1">
         <v>0.06</v>
@@ -4347,13 +4405,13 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="D38" s="1">
         <v>0.2</v>
@@ -4383,33 +4441,33 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N38" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P38" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O38" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q38" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="D39" s="1">
         <v>0.2</v>
@@ -4439,30 +4497,30 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N39" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P39" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O39" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q39" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>37</v>
@@ -4495,22 +4553,22 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N40" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P40" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O40" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -4521,7 +4579,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D41" s="1">
         <v>0.2</v>
@@ -4551,22 +4609,22 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N41" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P41" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O41" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q41" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
@@ -4607,30 +4665,30 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N42" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P42" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q42" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>27</v>
@@ -4663,33 +4721,33 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N43" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P43" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O43" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q43" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="D44" s="1">
         <v>0.2</v>
@@ -4719,22 +4777,22 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N44" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P44" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q44" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -4745,7 +4803,7 @@
         <v>41</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D45" s="1">
         <v>0.2</v>
@@ -4775,22 +4833,22 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N45" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P45" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O45" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q45" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -4801,7 +4859,7 @@
         <v>42</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D46" s="1">
         <v>0.2</v>
@@ -4831,33 +4889,33 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N46" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P46" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O46" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q46" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="D47" s="1">
         <v>0.2</v>
@@ -4887,33 +4945,33 @@
         <v>0.96</v>
       </c>
       <c r="N47" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P47" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O47" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q47" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="D48" s="1">
         <v>0.2</v>
@@ -4943,33 +5001,33 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N48" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P48" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O48" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q48" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="D49" s="1">
         <v>0.2</v>
@@ -4999,22 +5057,22 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N49" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P49" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O49" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q49" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -5055,22 +5113,22 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="N50" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P50" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="O50" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="Q50" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
@@ -5078,7 +5136,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>46</v>
@@ -5116,13 +5174,13 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="D52" s="1">
         <v>0.15</v>
@@ -5155,16 +5213,16 @@
         <v>0.96</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>48</v>
@@ -5175,13 +5233,13 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="D53" s="1">
         <v>0.15</v>
@@ -5214,16 +5272,16 @@
         <v>0.96</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R53" s="1" t="s">
         <v>48</v>
@@ -5234,13 +5292,13 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>635</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>637</v>
       </c>
       <c r="D54" s="1">
         <v>0.15</v>
@@ -5273,16 +5331,16 @@
         <v>0.96</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R54" s="1" t="s">
         <v>48</v>
@@ -5329,16 +5387,16 @@
         <v>0.96</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R55" s="1" t="s">
         <v>48</v>
@@ -5352,7 +5410,7 @@
         <v>52</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>53</v>
@@ -5396,7 +5454,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D57" s="1">
         <v>0.2</v>
@@ -5437,7 +5495,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>57</v>
@@ -5470,16 +5528,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>30</v>
@@ -5493,7 +5551,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>59</v>
@@ -5526,22 +5584,22 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O59" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
@@ -5549,7 +5607,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>46</v>
@@ -5582,16 +5640,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R60" s="1" t="s">
         <v>30</v>
@@ -5602,7 +5660,7 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>59</v>
@@ -5635,22 +5693,22 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R61" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
@@ -5658,10 +5716,10 @@
         <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="D62" s="1">
         <v>0.1</v>
@@ -5699,7 +5757,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>65</v>
@@ -5740,7 +5798,7 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>67</v>
@@ -5781,7 +5839,7 @@
         <v>68</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>44</v>
@@ -5822,7 +5880,7 @@
         <v>70</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>44</v>
@@ -5899,10 +5957,10 @@
         <v>0.97</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>74</v>
@@ -5949,10 +6007,10 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R68" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>76</v>
@@ -5963,7 +6021,7 @@
         <v>77</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>6</v>
@@ -5999,7 +6057,7 @@
         <v>0.96</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
@@ -6007,7 +6065,7 @@
         <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>6</v>
@@ -6051,7 +6109,7 @@
         <v>80</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>27</v>
@@ -6092,7 +6150,7 @@
         <v>81</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>57</v>
@@ -6133,10 +6191,10 @@
         <v>82</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="D73" s="1">
         <v>3</v>
@@ -6177,10 +6235,10 @@
         <v>84</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="D74" s="1">
         <v>3</v>
@@ -6221,10 +6279,10 @@
         <v>86</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="D75" s="1">
         <v>3</v>
@@ -6265,10 +6323,10 @@
         <v>87</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="D76" s="1">
         <v>2</v>
@@ -6309,10 +6367,10 @@
         <v>87</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="D77" s="1">
         <v>3</v>
@@ -6350,10 +6408,10 @@
         <v>89</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="D78" s="1">
         <v>3</v>
@@ -6386,7 +6444,7 @@
         <v>0.97</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>76</v>
@@ -6397,10 +6455,10 @@
         <v>90</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="D79" s="1">
         <v>3</v>
@@ -6438,7 +6496,7 @@
         <v>91</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>44</v>
@@ -6482,7 +6540,7 @@
         <v>93</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>44</v>
@@ -6523,10 +6581,10 @@
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D82" s="1">
         <v>0.5</v>
@@ -6549,10 +6607,10 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>6</v>
@@ -6585,7 +6643,7 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="S83" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
@@ -6593,7 +6651,7 @@
         <v>94</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>95</v>
@@ -6631,7 +6689,7 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D85" s="1">
         <v>0.5</v>
@@ -6657,7 +6715,7 @@
         <v>96</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>97</v>
@@ -6695,10 +6753,10 @@
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>97</v>
@@ -6736,7 +6794,7 @@
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>97</v>
@@ -6771,10 +6829,10 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>98</v>
@@ -6803,7 +6861,7 @@
         <v>99</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>98</v>
@@ -6847,10 +6905,10 @@
         <v>100</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="D91" s="1">
         <v>6</v>
@@ -6885,13 +6943,13 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="D92" s="1">
         <v>0.3</v>
@@ -6926,13 +6984,13 @@
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
@@ -6947,10 +7005,10 @@
         <v>18.559999999999999</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J93" s="1">
         <v>52</v>
@@ -6967,10 +7025,10 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D94" s="1">
         <v>1</v>
@@ -7005,7 +7063,7 @@
         <v>101</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>102</v>
@@ -7041,19 +7099,19 @@
         <v>0.90500000000000003</v>
       </c>
       <c r="N95" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="O95" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="O95" s="1" t="s">
+      <c r="P95" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q95" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="P95" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q95" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="R95" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
@@ -7061,7 +7119,7 @@
         <v>103</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>102</v>
@@ -7097,27 +7155,27 @@
         <v>0.90500000000000003</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O96" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="P96" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q96" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="P96" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q96" s="1" t="s">
+      <c r="R96" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="R96" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>102</v>
@@ -7153,7 +7211,7 @@
         <v>0.90500000000000003</v>
       </c>
       <c r="S97" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
@@ -7161,7 +7219,7 @@
         <v>104</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>105</v>
@@ -7205,7 +7263,7 @@
         <v>107</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>102</v>
@@ -7249,10 +7307,10 @@
         <v>109</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="D100" s="1">
         <v>3</v>
@@ -7285,30 +7343,30 @@
         <v>0.91</v>
       </c>
       <c r="N100" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O100" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="O100" s="1" t="s">
+      <c r="P100" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="R100" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="P100" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q100" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="R100" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>424</v>
+        <v>703</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>424</v>
+        <v>706</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D101" s="1">
         <v>5</v>
@@ -7337,13 +7395,13 @@
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>110</v>
+        <v>704</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>110</v>
+        <v>705</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D102" s="1">
         <v>5</v>
@@ -7376,16 +7434,16 @@
         <v>0.91</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>2</v>
@@ -7393,13 +7451,13 @@
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="D103" s="1">
         <v>12</v>
@@ -7432,27 +7490,27 @@
         <v>0.92</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q103" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D104" s="1">
         <v>15</v>
@@ -7485,18 +7543,18 @@
         <v>0.92</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D105" s="1">
         <v>4</v>
@@ -7529,30 +7587,30 @@
         <v>0.92</v>
       </c>
       <c r="N105" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q105" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="O105" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="Q105" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="R105" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D106" s="1">
         <v>8</v>
@@ -7585,27 +7643,27 @@
         <v>0.97</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q106" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D107" s="1">
         <v>18</v>
@@ -7632,18 +7690,18 @@
         <v>1.06</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D108" s="1">
         <v>4</v>
@@ -7670,27 +7728,27 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q108" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S108" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D109" s="1">
         <v>20</v>
@@ -7728,13 +7786,13 @@
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D110" s="1">
         <v>5</v>
@@ -7767,18 +7825,18 @@
         <v>0.95</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D111" s="1">
         <v>5</v>
@@ -7811,10 +7869,10 @@
         <v>0.98</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="S111" s="1" t="s">
         <v>74</v>
@@ -7822,13 +7880,13 @@
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D112" s="1">
         <v>4</v>
@@ -7861,19 +7919,19 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="N112" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="P112" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="O112" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="P112" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="Q112" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S112" s="1" t="s">
         <v>76</v>
@@ -7881,13 +7939,13 @@
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D113" s="1">
         <v>5</v>
@@ -7920,18 +7978,18 @@
         <v>1.07</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D114" s="1">
         <v>5</v>
@@ -7964,30 +8022,30 @@
         <v>0.97</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="Q114" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D115" s="1">
         <v>5</v>
@@ -8020,15 +8078,15 @@
         <v>0.98</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D116" s="1">
         <v>7</v>
@@ -8061,18 +8119,18 @@
         <v>0.98</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D117" s="1">
         <v>8</v>
@@ -8105,18 +8163,18 @@
         <v>0.93500000000000005</v>
       </c>
       <c r="S117" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D118" s="1">
         <v>10</v>
@@ -8152,18 +8210,18 @@
         <v>48</v>
       </c>
       <c r="S118" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D119" s="1">
         <v>1</v>
@@ -8196,30 +8254,30 @@
         <v>0.93</v>
       </c>
       <c r="N119" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O119" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="O119" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="P119" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="Q119" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="R119" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="R119" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D120" s="1">
         <v>5</v>
@@ -8252,18 +8310,18 @@
         <v>0.95</v>
       </c>
       <c r="S120" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D121" s="1">
         <v>5</v>
@@ -8301,13 +8359,13 @@
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D122" s="1">
         <v>7</v>
@@ -8340,18 +8398,18 @@
         <v>0.92</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D123" s="1">
         <v>5</v>
@@ -8384,18 +8442,18 @@
         <v>0.95</v>
       </c>
       <c r="S123" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D124" s="1">
         <v>5</v>
@@ -8428,18 +8486,18 @@
         <v>0.95</v>
       </c>
       <c r="S124" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D125" s="1">
         <v>3</v>
@@ -8472,30 +8530,30 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="N125" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O125" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="O125" s="1" t="s">
+      <c r="P125" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q125" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="P125" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q125" s="1" t="s">
+      <c r="R125" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="R125" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D126" s="1">
         <v>7</v>
@@ -8528,7 +8586,7 @@
         <v>0.94</v>
       </c>
       <c r="R126" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="S126" s="1" t="s">
         <v>49</v>
@@ -8536,13 +8594,13 @@
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D127" s="1">
         <v>6</v>
@@ -8575,18 +8633,18 @@
         <v>0.95</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D128" s="1">
         <v>7</v>
@@ -8619,18 +8677,18 @@
         <v>1.05</v>
       </c>
       <c r="S128" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D129" s="1">
         <v>10</v>
@@ -8663,7 +8721,7 @@
         <v>0.92</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S129" s="1" t="s">
         <v>0</v>
@@ -8671,13 +8729,13 @@
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D130" s="1">
         <v>5</v>
@@ -8710,33 +8768,33 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="N130" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P130" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="Q130" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="S130" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D131" s="1">
         <v>6</v>
@@ -8769,18 +8827,18 @@
         <v>0.94</v>
       </c>
       <c r="S131" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D132" s="1">
         <v>10</v>
@@ -8815,10 +8873,10 @@
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D133" s="1">
         <v>15</v>
@@ -8851,18 +8909,18 @@
         <v>0.93</v>
       </c>
       <c r="S133" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D134" s="1">
         <v>8</v>
@@ -8892,21 +8950,21 @@
         <v>0.98499999999999999</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="S134" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D135" s="1">
         <v>1.5</v>
@@ -8936,33 +8994,33 @@
         <v>0.92500000000000004</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P135" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q135" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="R135" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="S135" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="S135" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D136" s="1">
         <v>3</v>
@@ -8985,24 +9043,24 @@
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D138" s="1">
         <v>6</v>
@@ -9035,33 +9093,33 @@
         <v>0.93</v>
       </c>
       <c r="N138" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O138" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="O138" s="1" t="s">
+      <c r="P138" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q138" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="P138" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q138" s="1" t="s">
+      <c r="R138" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="S138" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="R138" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="S138" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D139" s="1">
         <v>3.5</v>
@@ -9094,16 +9152,16 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="N139" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q139" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="O139" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="Q139" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="R139" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S139" s="1" t="s">
         <v>32</v>
@@ -9111,13 +9169,13 @@
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D140" s="1">
         <v>3.5</v>
@@ -9150,27 +9208,27 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="N140" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q140" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="O140" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="Q140" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="R140" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D141" s="1">
         <v>3.5</v>
@@ -9203,18 +9261,18 @@
         <v>0.92</v>
       </c>
       <c r="S141" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D142" s="1">
         <v>4</v>
@@ -9247,18 +9305,18 @@
         <v>0.94</v>
       </c>
       <c r="S142" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D143" s="1">
         <v>0.5</v>
@@ -9291,18 +9349,18 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="S143" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D144" s="1">
         <v>18</v>
@@ -9335,27 +9393,27 @@
         <v>0.91</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q144" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R144" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D145" s="1">
         <v>2</v>
@@ -9390,13 +9448,13 @@
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D146" s="1">
         <v>2</v>
@@ -9431,24 +9489,24 @@
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D148" s="1">
         <v>18</v>
@@ -9475,27 +9533,27 @@
         <v>1.06</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q148" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="R148" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="S148" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="S148" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D149" s="1">
         <v>12</v>
@@ -9528,15 +9586,15 @@
         <v>0.92</v>
       </c>
       <c r="S149" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>73</v>
@@ -9577,13 +9635,13 @@
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="D151" s="1">
         <v>5</v>
@@ -9616,18 +9674,18 @@
         <v>0.93</v>
       </c>
       <c r="S151" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="D152" s="1">
         <v>13</v>
@@ -9660,15 +9718,15 @@
         <v>0.92</v>
       </c>
       <c r="S152" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>73</v>
@@ -9704,27 +9762,27 @@
         <v>0.92</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R153" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S153" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>73</v>
@@ -9760,33 +9818,33 @@
         <v>0.92</v>
       </c>
       <c r="N154" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="O154" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="O154" s="1" t="s">
+      <c r="P154" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q154" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="P154" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q154" s="1" t="s">
+      <c r="R154" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S154" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="R154" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="S154" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D155" s="1">
         <v>4</v>
@@ -9819,10 +9877,10 @@
         <v>0.95</v>
       </c>
       <c r="Q155" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R155" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S155" s="1" t="s">
         <v>76</v>
@@ -9830,10 +9888,10 @@
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>73</v>
@@ -9869,10 +9927,10 @@
         <v>0.95</v>
       </c>
       <c r="Q156" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S156" s="1" t="s">
         <v>76</v>
@@ -9880,10 +9938,10 @@
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>73</v>
@@ -9919,10 +9977,10 @@
         <v>0.93</v>
       </c>
       <c r="Q157" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="R157" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="R157" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="S157" s="1" t="s">
         <v>74</v>
@@ -9930,10 +9988,10 @@
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D158" s="1">
         <v>10</v>
@@ -9966,21 +10024,21 @@
         <v>0.92</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R158" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="S158" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D159" s="1">
         <v>10</v>
@@ -10013,21 +10071,21 @@
         <v>0.92</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="S159" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>73</v>
@@ -10063,10 +10121,10 @@
         <v>0.91</v>
       </c>
       <c r="Q160" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R160" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S160" s="1" t="s">
         <v>74</v>
@@ -10074,10 +10132,10 @@
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D161" s="1">
         <v>10</v>
@@ -10104,16 +10162,16 @@
         <v>0.92</v>
       </c>
       <c r="N161" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O161" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="O161" s="1" t="s">
+      <c r="P161" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="P161" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="R161" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S161" s="1" t="s">
         <v>0</v>
@@ -10121,10 +10179,10 @@
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>73</v>
@@ -10160,18 +10218,18 @@
         <v>0.93</v>
       </c>
       <c r="S162" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D163" s="1">
         <v>10</v>
@@ -10204,15 +10262,15 @@
         <v>0.93</v>
       </c>
       <c r="S163" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>73</v>
@@ -10245,30 +10303,30 @@
         <v>0.92</v>
       </c>
       <c r="N164" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="O164" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="O164" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="P164" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q164" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="R164" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="S164" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="S164" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>73</v>
@@ -10276,24 +10334,24 @@
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="D167" s="1">
         <v>15</v>
@@ -10326,33 +10384,33 @@
         <v>0.95</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P167" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="R167" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S167" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D168" s="1">
         <v>12</v>
@@ -10385,15 +10443,15 @@
         <v>0.91</v>
       </c>
       <c r="S168" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D169" s="1">
         <v>18</v>
@@ -10420,27 +10478,27 @@
         <v>1.06</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="R169" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="S169" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="S169" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="D170" s="1">
         <v>5</v>
@@ -10473,18 +10531,18 @@
         <v>0.92</v>
       </c>
       <c r="S170" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D171" s="1">
         <v>5</v>
@@ -10517,18 +10575,18 @@
         <v>0.93</v>
       </c>
       <c r="S171" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="D172" s="1">
         <v>5</v>
@@ -10561,18 +10619,18 @@
         <v>0.93</v>
       </c>
       <c r="S172" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="D173" s="1">
         <v>5</v>
@@ -10605,18 +10663,18 @@
         <v>0.93</v>
       </c>
       <c r="S173" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="D174" s="1">
         <v>5</v>
@@ -10649,18 +10707,18 @@
         <v>0.93</v>
       </c>
       <c r="S174" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D175" s="1">
         <v>5</v>
@@ -10693,18 +10751,18 @@
         <v>0.93</v>
       </c>
       <c r="S175" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D176" s="1">
         <v>6</v>
@@ -10737,33 +10795,33 @@
         <v>0.92</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O176" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P176" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="R176" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="S176" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D177" s="1">
         <v>5</v>
@@ -10796,10 +10854,10 @@
         <v>0.94</v>
       </c>
       <c r="Q177" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R177" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S177" s="1" t="s">
         <v>74</v>
@@ -10807,13 +10865,13 @@
     </row>
     <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D178" s="1">
         <v>5</v>
@@ -10846,10 +10904,10 @@
         <v>0.94</v>
       </c>
       <c r="Q178" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R178" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S178" s="1" t="s">
         <v>74</v>
@@ -10857,13 +10915,13 @@
     </row>
     <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D179" s="1">
         <v>5</v>
@@ -10896,10 +10954,10 @@
         <v>0.94</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R179" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S179" s="1" t="s">
         <v>74</v>
@@ -10907,10 +10965,10 @@
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D180" s="1">
         <v>5</v>
@@ -10943,10 +11001,10 @@
         <v>0.94</v>
       </c>
       <c r="Q180" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R180" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S180" s="1" t="s">
         <v>74</v>
@@ -10954,13 +11012,13 @@
     </row>
     <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D181" s="1">
         <v>12</v>
@@ -10993,18 +11051,18 @@
         <v>0.91</v>
       </c>
       <c r="S181" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D182" s="1">
         <v>12</v>
@@ -11037,18 +11095,18 @@
         <v>0.92</v>
       </c>
       <c r="S182" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D183" s="1">
         <v>18</v>
@@ -11075,27 +11133,27 @@
         <v>1.06</v>
       </c>
       <c r="N183" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q183" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="R183" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="S183" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="S183" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D184" s="1">
         <v>7</v>
@@ -11128,18 +11186,18 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="S184" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D185" s="1">
         <v>10</v>
@@ -11177,13 +11235,13 @@
     </row>
     <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="D186" s="1">
         <v>7</v>
@@ -11216,18 +11274,18 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="S186" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D187" s="1">
         <v>5</v>
@@ -11260,18 +11318,18 @@
         <v>0.93</v>
       </c>
       <c r="S187" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D188" s="1">
         <v>15</v>
@@ -11304,30 +11362,30 @@
         <v>0.92</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O188" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q188" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R188" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S188" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D189" s="1">
         <v>4</v>
@@ -11360,10 +11418,10 @@
         <v>0.94</v>
       </c>
       <c r="Q189" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R189" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S189" s="1" t="s">
         <v>74</v>
@@ -11371,13 +11429,13 @@
     </row>
     <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D190" s="1">
         <v>4</v>
@@ -11410,10 +11468,10 @@
         <v>0.94</v>
       </c>
       <c r="Q190" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R190" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S190" s="1" t="s">
         <v>74</v>
@@ -11421,13 +11479,13 @@
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D191" s="1">
         <v>15</v>
@@ -11460,18 +11518,18 @@
         <v>0.92</v>
       </c>
       <c r="S191" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D192" s="1">
         <v>8</v>
@@ -11504,15 +11562,15 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="S192" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B193" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D193" s="1">
         <v>18</v>
@@ -11539,27 +11597,27 @@
         <v>1.06</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q193" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="R193" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="S193" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="S193" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D194" s="1">
         <v>5</v>
@@ -11592,18 +11650,18 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="S194" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>565</v>
       </c>
       <c r="D195" s="1">
         <v>4</v>
@@ -11636,30 +11694,30 @@
         <v>0.92</v>
       </c>
       <c r="N195" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O195" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P195" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q195" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="R195" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="S195" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B196" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D196" s="1">
         <v>10</v>
@@ -11692,21 +11750,21 @@
         <v>0.92</v>
       </c>
       <c r="N196" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R196" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="S196" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B197" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D197" s="1">
         <v>10</v>
@@ -11739,24 +11797,24 @@
         <v>0.92</v>
       </c>
       <c r="N197" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R197" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="S197" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D198" s="1">
         <v>12</v>
@@ -11789,18 +11847,18 @@
         <v>0.91</v>
       </c>
       <c r="S198" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="D199" s="1">
         <v>0.7</v>
@@ -11833,30 +11891,30 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="N199" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="O199" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="O199" s="1" t="s">
+      <c r="Q199" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="Q199" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="R199" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S199" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C200" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="D200" s="1">
         <v>15</v>
@@ -11889,18 +11947,18 @@
         <v>0.93</v>
       </c>
       <c r="S200" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C201" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="D201" s="1">
         <v>12</v>
@@ -11933,18 +11991,18 @@
         <v>0.91</v>
       </c>
       <c r="S201" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D202" s="1">
         <v>18</v>
@@ -11971,27 +12029,27 @@
         <v>1.06</v>
       </c>
       <c r="N202" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q202" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="R202" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="S202" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="S202" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D203" s="1">
         <v>25</v>
@@ -12024,21 +12082,21 @@
         <v>0.93</v>
       </c>
       <c r="R203" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="S203" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D204" s="1">
         <v>12</v>
@@ -12071,18 +12129,18 @@
         <v>0.93</v>
       </c>
       <c r="S204" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D205" s="1">
         <v>5</v>
@@ -12115,18 +12173,18 @@
         <v>0.92</v>
       </c>
       <c r="S205" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D206" s="1">
         <v>5</v>
@@ -12159,18 +12217,18 @@
         <v>0.93</v>
       </c>
       <c r="S206" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D207" s="1">
         <v>15</v>
@@ -12203,30 +12261,30 @@
         <v>0.92</v>
       </c>
       <c r="N207" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q207" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R207" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S207" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D208" s="1">
         <v>5</v>
@@ -12259,18 +12317,18 @@
         <v>0.93</v>
       </c>
       <c r="S208" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D209" s="1">
         <v>4</v>
@@ -12303,18 +12361,18 @@
         <v>0.93</v>
       </c>
       <c r="S209" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D210" s="1">
         <v>5</v>
@@ -12347,18 +12405,18 @@
         <v>0.93</v>
       </c>
       <c r="S210" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D211" s="1">
         <v>5</v>
@@ -12391,10 +12449,10 @@
         <v>0.94</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S211" s="1" t="s">
         <v>74</v>
@@ -12402,13 +12460,13 @@
     </row>
     <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D212" s="1">
         <v>5</v>
@@ -12441,10 +12499,10 @@
         <v>0.94</v>
       </c>
       <c r="Q212" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R212" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S212" s="1" t="s">
         <v>74</v>
@@ -12452,13 +12510,13 @@
     </row>
     <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D213" s="1">
         <v>5</v>
@@ -12491,18 +12549,18 @@
         <v>0.93</v>
       </c>
       <c r="S213" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="D214" s="1">
         <v>1</v>
@@ -12540,13 +12598,13 @@
     </row>
     <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="D215" s="1">
         <v>4</v>
@@ -12579,18 +12637,18 @@
         <v>1.06</v>
       </c>
       <c r="S215" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D216" s="1">
         <v>5</v>
@@ -12625,13 +12683,13 @@
     </row>
     <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D217" s="1">
         <v>18</v>
@@ -12658,27 +12716,27 @@
         <v>1.06</v>
       </c>
       <c r="N217" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q217" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="R217" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="S217" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="S217" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D218" s="1">
         <v>5</v>
@@ -12711,18 +12769,18 @@
         <v>0.94</v>
       </c>
       <c r="S218" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D219" s="1">
         <v>5</v>
@@ -12755,18 +12813,18 @@
         <v>0.95</v>
       </c>
       <c r="S219" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D220" s="1">
         <v>2</v>
@@ -12801,13 +12859,13 @@
     </row>
     <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D221" s="1">
         <v>12</v>
@@ -12840,18 +12898,18 @@
         <v>0.92</v>
       </c>
       <c r="S221" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D222" s="1">
         <v>5</v>
@@ -12884,21 +12942,21 @@
         <v>0.98</v>
       </c>
       <c r="Q222" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R222" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D223" s="1">
         <v>25</v>
@@ -12933,13 +12991,13 @@
     </row>
     <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D224" s="1">
         <v>20</v>
@@ -12972,15 +13030,15 @@
         <v>0.97</v>
       </c>
       <c r="S224" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B225" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D225" s="1">
         <v>25</v>
@@ -13007,21 +13065,21 @@
         <v>0.91</v>
       </c>
       <c r="R225" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="S225" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D226" s="1">
         <v>6</v>
@@ -13054,21 +13112,21 @@
         <v>0.98</v>
       </c>
       <c r="Q226" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="R226" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D227" s="1">
         <v>1</v>
@@ -13103,13 +13161,13 @@
     </row>
     <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D228" s="1">
         <v>3</v>
@@ -13142,18 +13200,18 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="S228" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D229" s="1">
         <v>7</v>
@@ -13186,18 +13244,18 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="S229" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D230" s="1">
         <v>7</v>
@@ -13230,18 +13288,18 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="S230" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D231" s="1">
         <v>5</v>
@@ -13274,18 +13332,18 @@
         <v>0.93</v>
       </c>
       <c r="S231" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D232" s="1">
         <v>15</v>
@@ -13318,30 +13376,30 @@
         <v>0.92</v>
       </c>
       <c r="N232" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q232" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="R232" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S232" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D233" s="1">
         <v>4</v>
@@ -13374,10 +13432,10 @@
         <v>1</v>
       </c>
       <c r="Q233" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R233" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S233" s="1" t="s">
         <v>76</v>
@@ -13385,13 +13443,13 @@
     </row>
     <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D234" s="1">
         <v>4</v>
@@ -13424,18 +13482,18 @@
         <v>0.95</v>
       </c>
       <c r="S234" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C235" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>617</v>
       </c>
       <c r="D235" s="1">
         <v>6</v>
@@ -13468,30 +13526,30 @@
         <v>0.92</v>
       </c>
       <c r="N235" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O235" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P235" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="Q235" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="R235" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="S235" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B236" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D236" s="1">
         <v>10</v>
@@ -13524,35 +13582,35 @@
         <v>0.92</v>
       </c>
       <c r="N236" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R236" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="S236" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D238" s="1">
         <v>6</v>
@@ -13585,18 +13643,18 @@
         <v>0.93</v>
       </c>
       <c r="R238" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="S238" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D239" s="1">
         <v>30</v>
@@ -13629,21 +13687,21 @@
         <v>0.90500000000000003</v>
       </c>
       <c r="S239" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B240" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="C240" s="1" t="s">
+      <c r="E240" s="1" t="s">
         <v>678</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E240" s="1" t="s">
-        <v>680</v>
       </c>
       <c r="F240" s="1">
         <v>23.22</v>
@@ -13664,15 +13722,15 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="S240" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B241" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D241" s="1">
         <v>6</v>
@@ -13699,33 +13757,33 @@
         <v>1.06</v>
       </c>
       <c r="N241" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="O241" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="P241" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="Q241" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="O241" s="1" t="s">
+      <c r="R241" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="P241" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="Q241" s="1" t="s">
+      <c r="S241" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="R241" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="S241" s="1" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C242" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>698</v>
       </c>
       <c r="D242" s="1">
         <v>4</v>
@@ -13752,7 +13810,107 @@
         <v>0.93500000000000005</v>
       </c>
       <c r="S242" s="1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B243" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C243" s="1" t="s">
         <v>699</v>
+      </c>
+      <c r="D243" s="1">
+        <v>10</v>
+      </c>
+      <c r="E243" s="1">
+        <v>15</v>
+      </c>
+      <c r="H243" s="1">
+        <v>10</v>
+      </c>
+      <c r="I243" s="1">
+        <v>12</v>
+      </c>
+      <c r="J243" s="1">
+        <v>70</v>
+      </c>
+      <c r="K243" s="1">
+        <v>71</v>
+      </c>
+      <c r="L243" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="M243" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="N243" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="R243" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="S243" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F244" s="1">
+        <v>9.01</v>
+      </c>
+      <c r="G244" s="1">
+        <v>12.31</v>
+      </c>
+      <c r="H244" s="1">
+        <v>20</v>
+      </c>
+      <c r="I244" s="1">
+        <v>35</v>
+      </c>
+      <c r="J244" s="1">
+        <v>67</v>
+      </c>
+      <c r="K244" s="1">
+        <v>68</v>
+      </c>
+      <c r="L244" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="M244" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="N244" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="O244" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="P244" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q244" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="R244" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S244" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
